--- a/src/attributions/attributions_ig_traj_121.xlsx
+++ b/src/attributions/attributions_ig_traj_121.xlsx
@@ -1568,46 +1568,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.03083523163100796</v>
+        <v>-0.04703525404370638</v>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04174498564630241</v>
+        <v>0.09106748087177605</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3340890712440183</v>
+        <v>-0.06455148912250269</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07538811131812849</v>
+        <v>0.0724833461711228</v>
       </c>
       <c r="K3" t="n">
         <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02937788307094774</v>
+        <v>0.0222505308447555</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.09355157548324265</v>
+        <v>-0.03810750110102628</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1616,25 +1616,25 @@
         <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.05202039476038831</v>
+        <v>-0.01635179617791438</v>
       </c>
       <c r="T3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07284789488044252</v>
+        <v>0.03536436147245173</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1600048297650426</v>
+        <v>-0.05562518272439117</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
@@ -1643,25 +1643,25 @@
         <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1658499962892412</v>
+        <v>0.08906553722612184</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.05016615213777154</v>
+        <v>-0.07307536424639033</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.04975237186204653</v>
+        <v>-0.06843055680243486</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1673,76 +1673,76 @@
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.04146425212270768</v>
+        <v>0.01066510639491346</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.01119671521983376</v>
+        <v>-0.05183775091757554</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1732004230617574</v>
+        <v>-0.07126055230393148</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
         <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.003548843488206997</v>
+        <v>-0.1119071757849508</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1602893918359883</v>
+        <v>0.02170940113535964</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.1713037070962831</v>
+        <v>-0.2925990984714199</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0143613344990397</v>
+        <v>-0.01205056036672087</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.03263392798251144</v>
+        <v>0.01667788578171807</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.06350226687990182</v>
+        <v>0.03814933297049792</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
@@ -1754,49 +1754,49 @@
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.03840486306253919</v>
+        <v>0.0639406544356213</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.01382963015601583</v>
+        <v>-0.00175244553929521</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.2475647986768957</v>
+        <v>0.0229600431198007</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.1249483253771275</v>
+        <v>-0.1155163935269689</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1529509398489406</v>
+        <v>0.1217663226459648</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.2295229352607911</v>
+        <v>-0.1141612204974204</v>
       </c>
       <c r="BZ3" t="n">
         <v>-0</v>
@@ -1808,187 +1808,187 @@
         <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.05333659077376122</v>
+        <v>0.06260636964474914</v>
       </c>
       <c r="CE3" t="n">
         <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.02554777236608039</v>
+        <v>-0.02522841907597179</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0942378635213596</v>
+        <v>0.07391322603752849</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.01252178465876849</v>
+        <v>-0.03830864152145576</v>
       </c>
       <c r="CN3" t="n">
         <v>-0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.08558079141702575</v>
+        <v>0.0006998753902201133</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.2003026761762752</v>
+        <v>-0.03369807926920155</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.05672225587584839</v>
+        <v>0.0482782271509222</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.008919348763721538</v>
+        <v>-0.04587930223008137</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.07242009724372137</v>
+        <v>0.02907262584105477</v>
       </c>
       <c r="DA3" t="n">
         <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.03229514358621462</v>
+        <v>0.04318106193760388</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0003999297311450402</v>
+        <v>0.0004486409659823557</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.143390787534005</v>
+        <v>0.1501275818141756</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
         <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.0820824748181741</v>
+        <v>0.1015435587341974</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.02854838996336742</v>
+        <v>0.03565763923344176</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.1240187958282196</v>
+        <v>-0.1139212491396822</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.08641808916242283</v>
+        <v>0.0217426269642303</v>
       </c>
       <c r="DX3" t="n">
         <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.06943470712956525</v>
+        <v>0.1597808952079283</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.01826984326151871</v>
+        <v>-0.1047558005061543</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.03105958962594181</v>
+        <v>0.03889157110579548</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.01183743430367261</v>
+        <v>0.01347925346616585</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.01215455959163531</v>
+        <v>0.07044222108361077</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
@@ -1997,28 +1997,28 @@
         <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.01479993290516033</v>
+        <v>0.01169362688619833</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.05078646663636132</v>
+        <v>-0.005785236651695048</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.01319389902091402</v>
+        <v>0.1037113876316088</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
         <v>0</v>
@@ -2027,52 +2027,52 @@
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.06002507895606981</v>
+        <v>0.04447343354986644</v>
       </c>
       <c r="EY3" t="n">
         <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.01348947397834061</v>
+        <v>-0.04443380475000871</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.06323957992780097</v>
+        <v>0.04710310867783406</v>
       </c>
       <c r="FC3" t="n">
         <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.1099097587169768</v>
+        <v>0.1924767245921716</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.04737142968124559</v>
+        <v>0.03307426404282401</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.1144145078189097</v>
+        <v>-0.01208896257531599</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN3" t="n">
         <v>0</v>
@@ -2081,40 +2081,40 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.1378182153151359</v>
+        <v>0.1578835845624834</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.0003016147885223471</v>
+        <v>0.001787073910481285</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.00776144884348893</v>
+        <v>0.006909132503142903</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV3" t="n">
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.07819228461902696</v>
+        <v>0.1542349755912946</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1486576452799234</v>
+        <v>-0.00157795758566855</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
@@ -2123,16 +2123,16 @@
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,16 +2140,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2302575036937714</v>
+        <v>0.1832899861922002</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05078603153387848</v>
+        <v>-0.05299426314119793</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04635532134098364</v>
+        <v>-0.03759467346489867</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,25 +2161,25 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08761228869763653</v>
+        <v>0.1021055447961113</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0289833222761626</v>
+        <v>0.03978789316420071</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.02698925756170125</v>
+        <v>-0.01727802620461159</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -2188,76 +2188,76 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1165061175366519</v>
+        <v>0.03749483129862221</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03247318740745204</v>
+        <v>-0.03287741382938258</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02724334733304633</v>
+        <v>-0.02941078744884315</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.04446365859983335</v>
+        <v>-0.003227495904937403</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.02513056278600408</v>
+        <v>-0.06893264099736419</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.02774307591818302</v>
+        <v>-0.07311487596250088</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.04242596964713773</v>
+        <v>0.08080725491888031</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.02785262353005715</v>
+        <v>-0.03418783846834476</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.009750848983609048</v>
+        <v>0.04723996422514316</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,25 +2275,25 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3960883589520132</v>
+        <v>0.2638346563717948</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.01104321207208174</v>
+        <v>-0.06609248558088043</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1770961567831914</v>
+        <v>-0.1146243342284563</v>
       </c>
       <c r="AY4" t="n">
         <v>-0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01035901704576626</v>
+        <v>-0.01161840389580761</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.03552449993950425</v>
+        <v>-0.01172967416625127</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.06007351326953553</v>
+        <v>-0.01160349628910894</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.04151466358540695</v>
+        <v>-0.01396480135795126</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.08807036872032757</v>
+        <v>0.02616463623576232</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.01165668051349908</v>
+        <v>0.0655727291141382</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,25 +2356,25 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.2121447564760501</v>
+        <v>0.1841410478580203</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01309371832300805</v>
+        <v>-0.05484009857896763</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.001944215734213227</v>
+        <v>-0.02230060775619941</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2383,46 +2383,46 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.06380802182175586</v>
+        <v>-0.09425030941860514</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.01325302612157519</v>
+        <v>0.07742891229495</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.02337221471710008</v>
+        <v>0.01120957649298686</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.03799857381721142</v>
+        <v>-0.077456380872992</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.1007089265392869</v>
+        <v>0.101534230293178</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1510780504573677</v>
+        <v>0.03043203417896889</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2437,49 +2437,49 @@
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.0512325684298692</v>
+        <v>-0.1005868422190318</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.03897312527755572</v>
+        <v>0.08653976670183636</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.01805333982812926</v>
+        <v>0.01911910602877896</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.06924289595763221</v>
+        <v>-0.04034855501296484</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.005012415749629913</v>
+        <v>-0.005338289427166111</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0001468177834877075</v>
+        <v>0.00140682486738627</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,25 +2491,25 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.06249782188231712</v>
+        <v>-0.07297559985349038</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.03345910950843985</v>
+        <v>0.0409526943182236</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.009555110770285022</v>
+        <v>-0.03961966729433535</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,52 +2518,52 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.05400128891603025</v>
+        <v>0.01266160404063889</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.06760496560744261</v>
+        <v>0.04391460217019334</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.0185473820011884</v>
+        <v>-0.01435919713625229</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.03583153373325045</v>
+        <v>-0.06306858755810521</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.07176445337456486</v>
+        <v>0.06007910945220016</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.002352259343831362</v>
+        <v>0.02878386756820444</v>
       </c>
       <c r="EK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
@@ -2572,73 +2572,73 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.03866154423016713</v>
+        <v>-0.05221183837374824</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.03597425431184407</v>
+        <v>-0.04718407671717966</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.02450240253724206</v>
+        <v>-0.002630805267537254</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.05842249063694201</v>
+        <v>-0.1084878331849238</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.02009441960186877</v>
+        <v>0.08303349219135901</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.0365543677782427</v>
+        <v>0.01059885837305573</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.02774364315162035</v>
+        <v>-0.05892533311626915</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.04514260277722268</v>
+        <v>0.02449751681024459</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01776926562376622</v>
+        <v>0.008127478683241415</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,28 +2647,28 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.001825826116651833</v>
+        <v>0.0003379069882186234</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.001149091899991819</v>
+        <v>0.1196837329665326</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0005849783758498215</v>
+        <v>-0.0008192467954840231</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
         <v>0</v>
@@ -2677,31 +2677,31 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.005432083994183844</v>
+        <v>-0.0748903004751713</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.01779269507172356</v>
+        <v>0.0273617290272852</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04226659454195073</v>
+        <v>0.4387538002236921</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03982335646850642</v>
+        <v>0.0678841149037733</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02700569919961005</v>
+        <v>-0.2306519045584358</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,34 +2736,34 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01015353904153345</v>
+        <v>0.2963687542348266</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01836931254403487</v>
+        <v>-0.02658023430598876</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.002846016048880476</v>
+        <v>-0.02881773867676123</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.006722235979341709</v>
+        <v>0.1677014725130491</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2772,52 +2772,52 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01856916012482928</v>
+        <v>-0.1907463810067141</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01556837382702964</v>
+        <v>0.01385487583991153</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01888197986854415</v>
+        <v>-0.01635971733760566</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.01283403078454772</v>
+        <v>-0.3095896836578733</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01384091099452332</v>
+        <v>0.008469806802634459</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.006775412350403027</v>
+        <v>0.1105247420480467</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,37 +2826,37 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01299732763421728</v>
+        <v>0.06548392149134183</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.00380473984000372</v>
+        <v>-0.0713107626336329</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.04789190715024955</v>
+        <v>0.7245849421726819</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.05095069932202743</v>
+        <v>-0.2439538545697033</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.02274431913251646</v>
+        <v>-0.2652450396455956</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2871,22 +2871,22 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01485789141502011</v>
+        <v>0.01595222188283061</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01043514674447431</v>
+        <v>-0.03377441729915048</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.005628195499786752</v>
+        <v>-0.0514306478221803</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,37 +2895,37 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03473957109904671</v>
+        <v>0.03970479930808024</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01787871418239907</v>
+        <v>0.1214944850416319</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.004805546237739874</v>
+        <v>0.1393618010553539</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.01859575413674023</v>
+        <v>0.5440594128033291</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,37 +2934,37 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.02635093598763911</v>
+        <v>-0.01062847186892436</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.002964487970626785</v>
+        <v>-0.1663768412688858</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.006003998178021017</v>
+        <v>-0.2053184086367364</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01455343892773271</v>
+        <v>-0.05393094771091322</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0121064551771401</v>
+        <v>0.1607211354879187</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
@@ -2976,22 +2976,22 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.001236905306161458</v>
+        <v>-0.3070738713540654</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.008618804066517934</v>
+        <v>0.125060732232974</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.008405607146442201</v>
+        <v>0.1031538442723224</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
@@ -3000,28 +3000,28 @@
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.0004173875841133941</v>
+        <v>-0.1935294701132268</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0144311844218041</v>
+        <v>-0.05594079125663939</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.01483132157113863</v>
+        <v>0.158908030199164</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3033,52 +3033,52 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.01480538215692793</v>
+        <v>-0.08100468720511778</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01067504391092807</v>
+        <v>-0.1469767284407642</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.002997426811452797</v>
+        <v>0.03559781536964776</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.007698001232194517</v>
+        <v>-0.1398331850539515</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0169137013234216</v>
+        <v>0.0509138014557598</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.01180621298529644</v>
+        <v>0.03616625117927886</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,25 +3087,25 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.01511874549682356</v>
+        <v>-0.03058726055298461</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01424609086787244</v>
+        <v>0.002311733855020657</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.001653266811706399</v>
+        <v>0.1565037595664046</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,34 +3114,34 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.001780809623730443</v>
+        <v>-0.07942141630871057</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.005668939362516993</v>
+        <v>-0.1486370322548155</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.00572447860879882</v>
+        <v>0.04249662589282913</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.009051351219507824</v>
+        <v>-0.06712750041656018</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,25 +3150,25 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.01977327991938731</v>
+        <v>-0.2414265769869419</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.009493424030314803</v>
+        <v>0.1379416324901229</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.002948093779418281</v>
+        <v>-0.213300427999697</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,16 +3177,16 @@
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01409622038970752</v>
+        <v>-0.0997323024539436</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01424024028477985</v>
+        <v>0.1290498238617289</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
@@ -3195,34 +3195,34 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.01898180496853687</v>
+        <v>-0.2590123118196583</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02461766532841797</v>
+        <v>0.0720560464287068</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01185754676459494</v>
+        <v>0.1706170095706409</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.001633106359650043</v>
+        <v>0.02689304117737511</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
@@ -3231,40 +3231,40 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.001051428458389351</v>
+        <v>-0.001584785443845024</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.02825235460742026</v>
+        <v>-0.05816191837811869</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01462151883123232</v>
+        <v>-0.08475008127328525</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC5" t="n">
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.001790233667182859</v>
+        <v>0.1039421881254725</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
         <v>0</v>
@@ -3847,46 +3847,46 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2874670861388494</v>
+        <v>0.3296231726637203</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1113744813248131</v>
+        <v>-0.1540552126522502</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02129502590413603</v>
+        <v>-0.04274362672773798</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1514739439798997</v>
+        <v>0.2568949977460197</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03123381421525734</v>
+        <v>-0.05121901529936677</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.04486436200716118</v>
+        <v>-0.05938829239305846</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
         <v>-0</v>
@@ -3898,73 +3898,73 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1128028992751281</v>
+        <v>0.05814513882959889</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04158897311327331</v>
+        <v>-0.05731125464262141</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03893701180282703</v>
+        <v>-0.0832075884518642</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06875104660683833</v>
+        <v>-0.0425936252214675</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.04154616608915666</v>
+        <v>-0.111849663167545</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01318898407585734</v>
+        <v>-0.1128747151235889</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03186754704975895</v>
+        <v>0.1252876368161034</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.02663270975121796</v>
+        <v>-0.06844164367908895</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.009305417091302417</v>
+        <v>0.04946547418819387</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -3982,25 +3982,25 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.3865374802164924</v>
+        <v>0.374784696030341</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.02066416344908297</v>
+        <v>-0.152043260566325</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.2138196576241406</v>
+        <v>-0.2378001077652413</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
@@ -4009,16 +4009,16 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.01800418129857638</v>
+        <v>-0.02968297132602248</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.06606893808215498</v>
+        <v>-0.01850579452269361</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.09238408198349962</v>
+        <v>-0.004123114836703836</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03816550522985986</v>
+        <v>-0.007657240127037102</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.06991598004550273</v>
+        <v>0.04227011519996223</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.04680032591969624</v>
+        <v>0.06799155202855009</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,25 +4063,25 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2059657691702138</v>
+        <v>0.2692495498615653</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.01098557221437625</v>
+        <v>-0.07162915599480067</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.02982613276980506</v>
+        <v>-0.0725230956110675</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4090,22 +4090,22 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.06604058866426261</v>
+        <v>-0.1410594789977432</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01433713632589941</v>
+        <v>0.134415036724154</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.02881233315275288</v>
+        <v>0.01618655001513028</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,19 +4117,19 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.0346072614194412</v>
+        <v>-0.09651259955674195</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.1111493385802223</v>
+        <v>0.2056799508049196</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1374427577802044</v>
+        <v>0.08108740269095437</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4144,49 +4144,49 @@
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.05175062451639542</v>
+        <v>-0.1403556537145533</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.03577350748300505</v>
+        <v>0.1466866074647622</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.02328274640206962</v>
+        <v>0.02467326782940965</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.04771736249413293</v>
+        <v>-0.04888615716476859</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.003275716275160872</v>
+        <v>-0.01148927971123737</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.001110446921015418</v>
+        <v>-0.01808792242503779</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -4198,25 +4198,25 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.07005215648964851</v>
+        <v>-0.08824425710773874</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.032354013569855</v>
+        <v>0.04800161510437533</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.007332453962874238</v>
+        <v>-0.05002850678422954</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -4225,76 +4225,76 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.05200313091024676</v>
+        <v>0.03448791811809345</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.06062687371465929</v>
+        <v>0.05770721129899632</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.02150867881944668</v>
+        <v>-0.02062672145226321</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.02371207446839527</v>
+        <v>-0.09484703740750161</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.06456542969570377</v>
+        <v>0.1305645868615095</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.008077618525027747</v>
+        <v>0.0225088348393046</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.0498014412048861</v>
+        <v>-0.08481186223637052</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.03044230737251048</v>
+        <v>-0.09511580721931927</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.02854460684190254</v>
+        <v>0.007460485381939486</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4303,49 +4303,49 @@
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.06088880120825045</v>
+        <v>-0.1555881025304742</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.01597226790513694</v>
+        <v>0.146004486704523</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03058125123578752</v>
+        <v>0.009524071382179818</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.03215075035089877</v>
+        <v>-0.06920427367628643</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.04104556388902602</v>
+        <v>0.05840592388481116</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01665042453416223</v>
+        <v>-0.008879969553744245</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
@@ -4354,28 +4354,28 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.003959335320654948</v>
+        <v>0.006921475055926173</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.00787900942763247</v>
+        <v>0.157572784309168</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.02275905267125922</v>
+        <v>-0.01137363625605062</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
         <v>0</v>
@@ -4384,31 +4384,31 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.01752430293502626</v>
+        <v>-0.1156898718651184</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.05188988765706994</v>
+        <v>0.07654424715475341</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.06224943633368885</v>
+        <v>0.4025068550582929</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,25 +4994,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0114209267401579</v>
+        <v>-0.01303262204064907</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.02740243685190335</v>
+        <v>-0.1814475672826049</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01671256548445396</v>
+        <v>0.3901036331655288</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,79 +5021,79 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01502450176646141</v>
+        <v>-0.1076451944938191</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.001184291032769072</v>
+        <v>-0.007180889633451467</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.001556396622077524</v>
+        <v>0.147701349900364</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0109133616553189</v>
+        <v>-0.04564369830769243</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01836830858538081</v>
+        <v>0.04659004755523934</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.02035296746675229</v>
+        <v>-0.01549967698131931</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02225610772645462</v>
+        <v>-0.2424634602466643</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.009062274825080737</v>
+        <v>0.04135043636656003</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
         <v>-0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01252364605983017</v>
+        <v>0.1214964253099581</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -5102,16 +5102,16 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.00504138848206248</v>
+        <v>0.006395858371986256</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.006518174836278194</v>
+        <v>-0.08021806993467245</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.06901274306167544</v>
+        <v>0.5652777375698954</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -5129,10 +5129,10 @@
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.01334082641118218</v>
+        <v>-0.2688979729518705</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.01492540330220632</v>
+        <v>-0.240478883155907</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5141,40 +5141,40 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01777082046096212</v>
+        <v>-0.01801510372379138</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.009727269197194613</v>
+        <v>-0.0845265062478139</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.004726103043218043</v>
+        <v>-0.03452081430655007</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.03490764249113346</v>
+        <v>0.03828414556532017</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,13 +5183,13 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01983525758967593</v>
+        <v>0.1244255732804754</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01235869720408697</v>
+        <v>0.07878427064913843</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>0</v>
@@ -5198,25 +5198,25 @@
         <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.02703597504151779</v>
+        <v>0.3840121243773281</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.02403148486275934</v>
+        <v>-0.03036570244699117</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.01858641686547517</v>
+        <v>-0.08674990724606475</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>-0</v>
@@ -5228,22 +5228,22 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.002234446736254342</v>
+        <v>-0.1567066807345086</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.002360752079200103</v>
+        <v>0.02174884498902516</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01518875879815906</v>
+        <v>0.10423122031365</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5252,52 +5252,52 @@
         <v>-0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0092330499435115</v>
+        <v>-0.2120357973813613</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.005933552745769359</v>
+        <v>0.2793628904413246</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.03118092089990477</v>
+        <v>0.0331040107053388</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0004665478950981532</v>
+        <v>-0.1436626893469485</v>
       </c>
       <c r="CX9" t="n">
         <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.002164285582403092</v>
+        <v>0.01703849515883938</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.01801410187019785</v>
+        <v>0.1148085031799085</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
@@ -5309,49 +5309,49 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0001361144816858302</v>
+        <v>-0.109378348379075</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01749953784304399</v>
+        <v>-0.09415066028471029</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01387908731390689</v>
+        <v>0.1119493910704656</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.00100578117325801</v>
+        <v>-0.1143770189591608</v>
       </c>
       <c r="DP9" t="n">
         <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.01729127750131859</v>
+        <v>-0.03394021361867407</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.005484286883990138</v>
+        <v>0.02071078152718207</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,103 +5363,103 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.02190529090153009</v>
+        <v>0.01442970464216181</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.03121019965008268</v>
+        <v>-0.07980203819597292</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.01495338696032404</v>
+        <v>0.05733001046038776</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>4.40058778072375e-05</v>
+        <v>-0.02621432081799353</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.002716373875677202</v>
+        <v>-0.04318044673417041</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.006223908973884969</v>
+        <v>0.02728881097501138</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.008985119500760025</v>
+        <v>-0.07292036958535307</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.02272589096221852</v>
+        <v>-0.1818891993112179</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.03944972242948464</v>
+        <v>-0.1511008054538928</v>
       </c>
       <c r="EU9" t="n">
         <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.004265206278172327</v>
+        <v>-0.1729244454958219</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.003206415078600628</v>
+        <v>0.001693657894229192</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.01967251591599786</v>
+        <v>0.09075857087260235</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5471,34 +5471,34 @@
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02127645294242974</v>
+        <v>-0.1462999847568822</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.03155241481391572</v>
+        <v>0.155699452440295</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.00601853008126948</v>
+        <v>0.08787541428279669</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.005764667468911485</v>
+        <v>0.02581045727743503</v>
       </c>
       <c r="FR9" t="n">
         <v>0</v>
@@ -5507,25 +5507,25 @@
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.008476663023248385</v>
+        <v>-0.05954963291408526</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.03280955647058911</v>
+        <v>-0.08207360450573091</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.01225664623687978</v>
+        <v>-0.06625404748057324</v>
       </c>
       <c r="GA9" t="n">
         <v>0</v>
@@ -5537,13 +5537,13 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.006697259039169762</v>
+        <v>0.03294836149071864</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2652664475030307</v>
+        <v>0.4163796439156767</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09325340356073333</v>
+        <v>-0.2040002778799453</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.06988725101901165</v>
+        <v>-0.04473187228513793</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5575,25 +5575,25 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1605030235446298</v>
+        <v>0.3752560386547648</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.04710822884591285</v>
+        <v>-0.1224565576376072</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.08514537463084741</v>
+        <v>-0.07639689405215749</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
@@ -5605,73 +5605,73 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06431317181450134</v>
+        <v>0.09693978725821456</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01635446035742453</v>
+        <v>-0.06767818708622028</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03294969041300178</v>
+        <v>-0.1103261831697296</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.07944423913867073</v>
+        <v>-0.1124112665788822</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.0397042123027938</v>
+        <v>-0.07582709557273878</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0008109963619231852</v>
+        <v>-0.1017630366015979</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01742706391422246</v>
+        <v>0.124771814108236</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.02631346826749787</v>
+        <v>-0.09778126686047037</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.05340751852325941</v>
+        <v>0.04723460025279644</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -5680,34 +5680,34 @@
         <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3298064580889729</v>
+        <v>0.394740332085769</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.006624944764529754</v>
+        <v>-0.19879789019748</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1140736179420841</v>
+        <v>-0.2721656133019321</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.02030331822467515</v>
+        <v>-0.04351158936855416</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.03384676526644614</v>
+        <v>-0.02148763348931552</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1036884694588265</v>
+        <v>-0.01484098588222163</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,22 +5743,22 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.07850916575384327</v>
+        <v>-0.02016797120469295</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.06521045282843832</v>
+        <v>0.06221387516072648</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.08048964616927427</v>
+        <v>0.02036710770300797</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,49 +5770,49 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1485442861897867</v>
+        <v>0.3225978055702576</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.002508761288223753</v>
+        <v>-0.1748629511136814</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.03051742144025043</v>
+        <v>-0.1074711416331629</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.05752507748863129</v>
+        <v>-0.1493336633443407</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.006065318679843465</v>
+        <v>0.1669857318271202</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.0004252281769985802</v>
+        <v>0.009437431033570358</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
@@ -5824,22 +5824,22 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.04339387129406846</v>
+        <v>-0.09130581854775076</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.08630849986522827</v>
+        <v>0.256480098537918</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.0832420540637121</v>
+        <v>0.1272656886519231</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
         <v>-0</v>
@@ -5851,25 +5851,25 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.03931765052321663</v>
+        <v>-0.142975193384505</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.02371364483347937</v>
+        <v>0.1851649094994135</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.001915230437197968</v>
+        <v>0.01591783369274805</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
@@ -5878,22 +5878,22 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.0004375120734241249</v>
+        <v>-0.1488205646202565</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01615065637976668</v>
+        <v>0.08193475906580658</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.01487349237295285</v>
+        <v>-0.08732204800227261</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5905,103 +5905,103 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.05139983726536106</v>
+        <v>-0.07549954706557929</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.05461472931191981</v>
+        <v>0.09023596693852917</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.004989343966424962</v>
+        <v>-0.009624929771615479</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.03538655913676677</v>
+        <v>0.03914735078133072</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.03182348403502251</v>
+        <v>0.02857826458407612</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.01354774312725723</v>
+        <v>0.01219951936165447</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02713376799883064</v>
+        <v>-0.08987752719156988</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.07590011708084718</v>
+        <v>0.1238023846981341</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03578956315362165</v>
+        <v>0.0298953164394387</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.04834918944509249</v>
+        <v>-0.08095078771802035</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.04144476314900959</v>
+        <v>-0.1297197590463707</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01040967670143023</v>
+        <v>-0.03050445592059803</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
@@ -6010,76 +6010,76 @@
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.04802192912613931</v>
+        <v>-0.1597215199419307</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.01856460359664011</v>
+        <v>0.1912521311153617</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01173117629432144</v>
+        <v>0.0009540625720578916</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0405729457343973</v>
+        <v>-0.1084449721289497</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.04545136167327622</v>
+        <v>0.1239480420543421</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02195954387739732</v>
+        <v>-0.01135986486207753</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.001390178938890903</v>
+        <v>0.009281119063868522</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.01088834345498924</v>
+        <v>0.1615269195816717</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.04189746052114594</v>
+        <v>-0.02933274889275689</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
@@ -6091,31 +6091,31 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.006303847694071393</v>
+        <v>-0.1102586117589336</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.01927570199074076</v>
+        <v>0.0935806602639412</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6689,46 +6689,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2813035719948727</v>
+        <v>0.1342757826556876</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0301008823231791</v>
+        <v>-0.03967484667465901</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.05643782752801008</v>
+        <v>-0.047255566457566</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1449406442154503</v>
+        <v>0.1247052862313151</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01227820440265649</v>
+        <v>-0.02077065313783184</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05214580352960676</v>
+        <v>-0.06004793771139563</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6740,76 +6740,76 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04178432427669106</v>
+        <v>0.03403250115685673</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.02043399758191116</v>
+        <v>-0.006826116560858176</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03999173490385394</v>
+        <v>-0.005565845234103491</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.04844257036043886</v>
+        <v>-0.01685763111074716</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.01199536932348555</v>
+        <v>-0.05774241751346948</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.005327766004050346</v>
+        <v>-0.07817665841013803</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.0148863883364908</v>
+        <v>0.04135626026960884</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.01167318656378591</v>
+        <v>-0.004370168415885798</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.03011800953279444</v>
+        <v>0.03905529185903549</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6827,43 +6827,43 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2594349257693344</v>
+        <v>0.1564423869773919</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.03112393365565282</v>
+        <v>-0.007111845929371458</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.05296356718650179</v>
+        <v>-0.09542267543937714</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.05950022986860797</v>
+        <v>-0.03917339689565478</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.05342703258022106</v>
+        <v>-0.009873997987743516</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.04975569349601068</v>
+        <v>-0.01204930834999856</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,19 +6881,19 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.106985337916301</v>
+        <v>0.03026435844479891</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01641749343003522</v>
+        <v>0.01947728916840046</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.09260111423073636</v>
+        <v>0.05611009239326008</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6908,76 +6908,76 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1307778550860325</v>
+        <v>0.1288817978251809</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.02320385709261587</v>
+        <v>-0.03820017863880809</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.02381837787731442</v>
+        <v>-0.01578196340958453</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.05267134566128882</v>
+        <v>-0.04168137027207088</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.005832734112573052</v>
+        <v>0.03919552041920702</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.005641751575165319</v>
+        <v>0.02174822804017522</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.05886561677130826</v>
+        <v>-0.05535210717660182</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.03483614577236063</v>
+        <v>0.03993730303716059</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.06252193968245229</v>
+        <v>0.0335159015240873</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,19 +6986,19 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.03537030496982597</v>
+        <v>-0.03912525828454212</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.006124552125493847</v>
+        <v>0.0433263957802615</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.002955863352439839</v>
+        <v>0.02547000584407275</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7007,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
@@ -7016,73 +7016,73 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.009049605335281114</v>
+        <v>-0.0003258051571426022</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.05063832496443729</v>
+        <v>0.00914580504964534</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.007324616173862491</v>
+        <v>-0.006124351925796613</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.062938030785407</v>
+        <v>-0.03991083570208818</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.003870150912557851</v>
+        <v>-0.0213779788329482</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01715135228154514</v>
+        <v>-0.01531760991979086</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.001620471671114557</v>
+        <v>0.04238425775678643</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.00997841698006505</v>
+        <v>0.01972644230663211</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.03203509119809108</v>
+        <v>-0.06118491985756788</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
@@ -7091,22 +7091,22 @@
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.03387613475128066</v>
+        <v>0.007891056157782831</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0.001585720219689498</v>
+        <v>0.02893097962195065</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.04901037069550478</v>
+        <v>0.04513457475773532</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
@@ -7115,7 +7115,7 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,19 +7124,19 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.02368006165593776</v>
+        <v>-0.03210221107597389</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.006879093251294921</v>
+        <v>0.0447269295332429</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02384752590249433</v>
+        <v>-0.008190651925803798</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
@@ -7145,22 +7145,22 @@
         <v>-0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.03412589096124122</v>
+        <v>-0.04708678232759928</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0001089485766206362</v>
+        <v>0.05015285510703023</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.01320349637276338</v>
+        <v>0.01439121254656846</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7169,25 +7169,25 @@
         <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0149542454249308</v>
+        <v>-0.002102311632746347</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.01884184398715685</v>
+        <v>0.003952372824172428</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.0357610994547067</v>
+        <v>-0.02527212268180276</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,31 +7196,31 @@
         <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.02803855844894806</v>
+        <v>0.01691956722382474</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.01376656434050059</v>
+        <v>0.05083773509656869</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.007241233376714142</v>
+        <v>-0.05069353223879568</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
@@ -7232,28 +7232,28 @@
         <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.004899291516374995</v>
+        <v>-0.01836987922747576</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.0186763988837574</v>
+        <v>0.007330420139009674</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1753325542458682</v>
+        <v>0.174478842369749</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.001861025648660907</v>
+        <v>-0.04144901042085377</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1201682660389519</v>
+        <v>-0.1267912077971837</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7285,37 +7285,37 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1168889493713425</v>
+        <v>0.3303171761512816</v>
       </c>
       <c r="L13" t="n">
         <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.01017045448786457</v>
+        <v>-0.09647810591724895</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.08542626605887788</v>
+        <v>-0.1175868999652359</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.008446767148017184</v>
+        <v>0.07503975655227844</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
@@ -7324,37 +7324,37 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01278187809399203</v>
+        <v>-0.07235077454018778</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.002970754225196949</v>
+        <v>-0.005628909027437738</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.02394926874866394</v>
+        <v>-0.02683181032311454</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01781980329618022</v>
+        <v>-0.2093013860391321</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.009280291295394521</v>
+        <v>-0.03949539815828559</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,28 +7363,28 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.003413801094535957</v>
+        <v>0.02698788062332071</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01244339580283066</v>
+        <v>-0.009244415801575702</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.02616287028459998</v>
+        <v>-0.02344256326774017</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,37 +7393,37 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1234868949431828</v>
+        <v>0.4109888796755349</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.005904159878943866</v>
+        <v>-0.1266299632621384</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.0617998178080619</v>
+        <v>-0.1030469045969443</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0579982268392056</v>
+        <v>-0.07936886362355035</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.02605781511664183</v>
+        <v>-0.08773568225441893</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.04952963543871915</v>
+        <v>-0.0389523222560061</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.05518064957611164</v>
+        <v>0.1330436717393748</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -7459,16 +7459,16 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.03374109603009773</v>
+        <v>0.07342477472382317</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.006923230405654165</v>
+        <v>-0.00379958294834209</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
         <v>0</v>
@@ -7477,19 +7477,19 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.05694431402149773</v>
+        <v>0.2678748415944099</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.00878505706844354</v>
+        <v>-0.05172951163299713</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.0137865728751884</v>
+        <v>-0.04168373657739333</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,67 +7498,67 @@
         <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD13" t="n">
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.03215815943760334</v>
+        <v>-0.05958964371256111</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.004434494349291136</v>
+        <v>0.04117746511200641</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.02646885193407263</v>
+        <v>0.05472550722600986</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.02154523065644725</v>
+        <v>-0.2274591676325248</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01984179989931486</v>
+        <v>0.1428753107660158</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01176309421974564</v>
+        <v>0.07267639868828193</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.02096775553385949</v>
+        <v>-0.05038574432753376</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
@@ -7567,10 +7567,10 @@
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.004598259934741873</v>
+        <v>0.01925330834448611</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.02479488552370201</v>
+        <v>0.05940478310713408</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7582,25 +7582,25 @@
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.00942792377255054</v>
+        <v>0.01433729055358203</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001745953236460921</v>
+        <v>-0.0293997212346517</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.003802847433232294</v>
+        <v>-0.001367782431143341</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>-0</v>
@@ -7609,118 +7609,118 @@
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.02257252574968996</v>
+        <v>-0.08859332234811762</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01153485178943712</v>
+        <v>0.06423165069586634</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.006552027293018942</v>
+        <v>0.000375969394743544</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.001428693419632627</v>
+        <v>0.04005598453323687</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.0113888537677719</v>
+        <v>-0.01422987406327267</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.006446938993383253</v>
+        <v>-0.05936552018947529</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.01541279637381846</v>
+        <v>0.04916102945361696</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.006183279215854137</v>
+        <v>-0.007815370506523516</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.016938949630433</v>
+        <v>0.02698671359498315</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.01768352447244188</v>
+        <v>0.009683560396128377</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0005301889719515236</v>
+        <v>-0.03912535894147016</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.03615955052527879</v>
+        <v>0.05214851045317084</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.0236515397506165</v>
+        <v>-0.06739984964739432</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,79 +7729,79 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.001030799584953018</v>
+        <v>0.0150785992854734</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.02870306760235427</v>
+        <v>0.0552844047321437</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.002023748522333679</v>
+        <v>-0.05227630282541201</v>
       </c>
       <c r="FI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.02117964532220485</v>
+        <v>0.03101400592166563</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.01691733208547199</v>
+        <v>0.03434694006940268</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.0102355319626828</v>
+        <v>-0.01781511471390874</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.0214387972297884</v>
+        <v>-0.07785909888902053</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.001205723560567617</v>
+        <v>0.00452072824780483</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
         <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.02293660569364711</v>
+        <v>0.00969624501062041</v>
       </c>
       <c r="GA13" t="n">
         <v>-0</v>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.0188488363080928</v>
+        <v>-0.02212723997940815</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7827,28 +7827,28 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3345422045462771</v>
+        <v>0.2046570568045433</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1040163273759496</v>
+        <v>-0.1391635265088232</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.05689265839859305</v>
+        <v>0.1642240210055048</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -7860,22 +7860,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2614667340631677</v>
+        <v>0.1989677382213334</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1237982883111269</v>
+        <v>-0.1527060369184444</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1247101020966574</v>
+        <v>0.09332410777899654</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -7887,19 +7887,19 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09688481565730274</v>
+        <v>0.03678761588890494</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.02582500224957221</v>
+        <v>-0.04709897140511093</v>
       </c>
       <c r="W14" t="n">
-        <v>0.03479458580762092</v>
+        <v>-0.04232896098443257</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>-0</v>
@@ -7911,79 +7911,79 @@
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.06004206032099968</v>
+        <v>0.04169451288128199</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.03800396211726926</v>
+        <v>0.1198136114214554</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.03052996765202319</v>
+        <v>0.0438756101125208</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.01928273281468286</v>
+        <v>0.04289646507611577</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.03078338412302969</v>
+        <v>-0.05927434488464093</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.06248062317465185</v>
+        <v>0.0002574403764750146</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.1529712139775669</v>
+        <v>0.1815730724655879</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.01858769403671884</v>
+        <v>-0.2317369779039581</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1708608151468087</v>
+        <v>-0.01095831038251931</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,16 +7992,16 @@
         <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0923004019583504</v>
+        <v>-0.001130502493756582</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.03984387068528213</v>
+        <v>0.1227698334268079</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.08900320377887121</v>
+        <v>0.07453582658333616</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
@@ -8016,49 +8016,49 @@
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.03816941572154151</v>
+        <v>-0.06788467592370474</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.05536851891374819</v>
+        <v>-0.07743821907492983</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1198218264601084</v>
+        <v>-0.1309883022584341</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.05954179341908349</v>
+        <v>0.1040804621528268</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0.02141594148381698</v>
+        <v>-0.1085156542285857</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.1117756655233817</v>
+        <v>-0.01275830279656665</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
@@ -8067,28 +8067,28 @@
         <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF14" t="n">
-        <v>-0.06959294209998884</v>
+        <v>-0.07832564682673127</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.02686093877623242</v>
+        <v>0.07135817575842671</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0004054989506993912</v>
+        <v>-0.04327651232711442</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8097,19 +8097,19 @@
         <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.01418004503149746</v>
+        <v>-0.007151148316827923</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.003704657935527651</v>
+        <v>0.1652076682098198</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.1186674801633818</v>
+        <v>0.007519312428672886</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
@@ -8118,34 +8118,34 @@
         <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0.05369284244981106</v>
+        <v>-0.05779338323976645</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.02648432469705512</v>
+        <v>0.06721353446840408</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.02319440181703224</v>
+        <v>-0.05769385527764437</v>
       </c>
       <c r="DA14" t="n">
         <v>-0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>0</v>
@@ -8154,16 +8154,16 @@
         <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0.03659946683637923</v>
+        <v>-0.01125307929713036</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.04330106983779596</v>
+        <v>0.02006291002408327</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.0056095734747765</v>
+        <v>-0.01911323884671937</v>
       </c>
       <c r="DJ14" t="n">
         <v>0</v>
@@ -8175,31 +8175,31 @@
         <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
         <v>-0</v>
       </c>
       <c r="DP14" t="n">
-        <v>-0.001868307312742693</v>
+        <v>-0.01811503225790511</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.02712015548731022</v>
+        <v>0.06966897874401506</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.1420395710614809</v>
+        <v>-0.06457514737998893</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
       </c>
       <c r="DT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
@@ -8208,16 +8208,16 @@
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.06473487613125521</v>
+        <v>0.02306792157768963</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.002457176101492261</v>
+        <v>0.002836824704821441</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.05875099378788502</v>
+        <v>0.07843873381304853</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
@@ -8232,46 +8232,46 @@
         <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0.1110914001496662</v>
+        <v>-0.04259690716461582</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.04635818549333129</v>
+        <v>0.01440926960917821</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.05896696643402607</v>
+        <v>0.01298690560050956</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
         <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>-0.006860286306501331</v>
+        <v>-0.04952080273176031</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.030564743052281</v>
+        <v>0.07976747118282944</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02856841084114657</v>
+        <v>0.03088273895205181</v>
       </c>
       <c r="ET14" t="n">
         <v>0</v>
@@ -8280,79 +8280,79 @@
         <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>-0.06724749697577918</v>
+        <v>-0.06279178689186302</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.04259430827403628</v>
+        <v>0.1039865954783983</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.02112461941074566</v>
+        <v>-0.04352554438357284</v>
       </c>
       <c r="FC14" t="n">
         <v>0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0.004725861477240727</v>
+        <v>-0.01953607261565314</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.005285212820973009</v>
+        <v>0.05611485805274248</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.07268587174485637</v>
+        <v>-0.03833534244464248</v>
       </c>
       <c r="FL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0.004240599187395422</v>
+        <v>-0.0002425550803640829</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.007104763743604158</v>
+        <v>-0.009901281984594551</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.09031323925689508</v>
+        <v>0.2642630620146642</v>
       </c>
       <c r="FU14" t="n">
         <v>0</v>
@@ -8361,22 +8361,22 @@
         <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.04626409388790098</v>
+        <v>-0.02756181751235361</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.05480273634979909</v>
+        <v>0.147349977541285</v>
       </c>
       <c r="GC14" t="n">
         <v>-0</v>
@@ -8399,19 +8399,19 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.185761519164108</v>
+        <v>0.2373337824054026</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.08280529374313922</v>
+        <v>-0.04664687109060651</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05906482528137331</v>
+        <v>-0.1340200125569248</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
@@ -8426,34 +8426,34 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1296497095568202</v>
+        <v>0.3315054476781985</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05609002565123491</v>
+        <v>-0.1098442723696418</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.03579135002131095</v>
+        <v>-0.08628771016387786</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01864672818254303</v>
+        <v>0.04872839620026031</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
@@ -8462,40 +8462,40 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.02887223281028661</v>
+        <v>-0.03340991195670458</v>
       </c>
       <c r="X15" t="n">
-        <v>0.02786397998979286</v>
+        <v>0.008096385628725463</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0305368007271461</v>
+        <v>-0.01956221671455853</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02202576027203309</v>
+        <v>-0.1385505748666266</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.003733405023159691</v>
+        <v>0.01043333309798664</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
@@ -8504,25 +8504,25 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.02968125502208196</v>
+        <v>0.04047913756227129</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.01786262120572332</v>
+        <v>-0.03809372585761372</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.02616291587461859</v>
+        <v>-0.02875975100417511</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8531,118 +8531,118 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1149478478685116</v>
+        <v>0.2745906257057886</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.0609388444850836</v>
+        <v>-0.1416871081255964</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.04359743020474337</v>
+        <v>-0.1303191517975555</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC15" t="n">
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.04113471601615659</v>
+        <v>0.008643997258531584</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.033586889642026</v>
+        <v>-0.06500036801438434</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.008106854990944429</v>
+        <v>-0.02634758994888761</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.05040382219578231</v>
+        <v>0.05444417493742189</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.02459522723025488</v>
+        <v>0.06717108733144284</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01557470893925633</v>
+        <v>0.03110582372546847</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.06765178711632917</v>
+        <v>0.162188570237383</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.03238911692027842</v>
+        <v>-0.04971851313415511</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.01062193215397759</v>
+        <v>-0.04817218318348154</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD15" t="n">
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.02639414156272516</v>
+        <v>-0.06009311427689332</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
@@ -8651,10 +8651,10 @@
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.008559142952868666</v>
+        <v>0.04657745749659409</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.01613051095244695</v>
+        <v>0.0473388649676917</v>
       </c>
       <c r="CJ15" t="n">
         <v>-0</v>
@@ -8663,25 +8663,25 @@
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.001681295693012171</v>
+        <v>-0.1402564251143357</v>
       </c>
       <c r="CO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP15" t="n">
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.01275195504509536</v>
+        <v>0.1663840163365967</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.02093154650694527</v>
+        <v>0.02888167853639684</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
@@ -8690,25 +8690,25 @@
         <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.01952888184489697</v>
+        <v>-0.05969681219856627</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.004553180121479291</v>
+        <v>0.02477936644056983</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.02295379872539117</v>
+        <v>0.05340759886381242</v>
       </c>
       <c r="DB15" t="n">
         <v>0</v>
@@ -8723,76 +8723,76 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.009446839789090784</v>
+        <v>-0.02083197696270756</v>
       </c>
       <c r="DG15" t="n">
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.008389746392797848</v>
+        <v>-0.009575962464975501</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0.004198287361923691</v>
+        <v>0.01331555364932408</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
       </c>
       <c r="DL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.02386988757301259</v>
+        <v>-0.04542119480032425</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.02125622512683335</v>
+        <v>0.02420069833244502</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.02144786251296666</v>
+        <v>0.05889706618060261</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW15" t="n">
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.005336672732941069</v>
+        <v>0.009052221199594909</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.02320332016238783</v>
+        <v>-0.03972497463145754</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0.01488335116879579</v>
+        <v>0.02351453101027287</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
         <v>0</v>
@@ -8801,64 +8801,64 @@
         <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.01621237883264771</v>
+        <v>-0.01691858519304042</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.01577216402764448</v>
+        <v>-0.01511575908304665</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.007292625230345929</v>
+        <v>0.04132552207182115</v>
       </c>
       <c r="EL15" t="n">
         <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0006805769808963989</v>
+        <v>-0.01247909489221269</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.0091960118702764</v>
+        <v>-0.0351153914092676</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.02677545493915625</v>
+        <v>-0.04888710252002696</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
         <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.01688998410672381</v>
+        <v>-0.06777234964664682</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
@@ -8867,13 +8867,13 @@
         <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.001741843322154773</v>
+        <v>0.02912177892940906</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.0234164705170184</v>
+        <v>0.04570943807231771</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
@@ -8885,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.02039740211811467</v>
+        <v>-0.05752168489926519</v>
       </c>
       <c r="FI15" t="n">
         <v>-0</v>
@@ -8894,25 +8894,25 @@
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.03842939906323027</v>
+        <v>0.05886615091126102</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.01951696093881562</v>
+        <v>-0.02431818055466254</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.002203766585031614</v>
+        <v>-0.004117442018878573</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
@@ -8921,43 +8921,43 @@
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.001105556594987681</v>
+        <v>0.003514809466212202</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.01600898399904726</v>
+        <v>-0.01279937676912598</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.02248658517898526</v>
+        <v>-0.0420893872409336</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.02490499780259479</v>
+        <v>0.02395882063395312</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>0</v>
